--- a/templates/cimb-jompay.xlsx
+++ b/templates/cimb-jompay.xlsx
@@ -9,24 +9,34 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <numFmts count="1">
+    <numFmt numFmtId="195" formatCode="0_);[Red]\(0\)"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF555555"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -35,13 +45,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
+        <fgColor rgb="FF969696"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -73,13 +77,45 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+  <cellXfs count="13">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="195" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -90,16 +126,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <col min="1" max="1" width="21.3" customWidth="1"/>
-  <col min="2" max="2" width="22.4" customWidth="1"/>
-  <col min="3" max="3" width="22.6" customWidth="1"/>
+  <col min="1" max="1" width="21.29" customWidth="1"/>
+  <col min="2" max="2" width="22.43" customWidth="1"/>
+  <col min="3" max="3" width="22.57" customWidth="1"/>
   <col min="4" max="4" width="32" customWidth="1"/>
-  <col min="5" max="5" width="22.4" customWidth="1"/>
+  <col min="5" max="5" width="22.43" customWidth="1"/>
   <sheetData>
-    <row r="1" ht="0.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="0.75" customHeight="1" hidden="1">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
@@ -109,75 +145,82 @@
           <t xml:space="preserve">40</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">20</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Length: 8 (Num Only)</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Length: 40 (Num Only)</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Length: 20 (Char Only)</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Length: 30 (Char Only)</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Length: 18 (Num Only)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">*JomPAY Biller Code</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">*Source Account</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">*Ref-1</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ref-2</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">*Amount</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="12"/>
     </row>
   </sheetData>
 </worksheet>
